--- a/Checklist BMP - Onboarding - Capt.xlsx
+++ b/Checklist BMP - Onboarding - Capt.xlsx
@@ -1494,7 +1494,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BCP87"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="27" customHeight="1"/>
   <cols>
     <col width="30.5703125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1635,17 +1635,25 @@
       <c r="F4" s="83" t="n"/>
       <c r="G4" s="83" t="n"/>
       <c r="H4" s="121" t="n"/>
-      <c r="I4" s="122" t="n"/>
-      <c r="J4" s="123" t="n"/>
+      <c r="I4" s="122" t="inlineStr">
+        <is>
+          <t>grant_type=client_credentials&amp;client_id={BMP_CLIENT_ID}&amp;scope=api.ext&amp;client_assertion={JWT RS256}&amp;client_assertion_type=urn:ietf:params:oauth:client-assertion-type:jwt-bearer</t>
+        </is>
+      </c>
+      <c r="J4" s="123" t="inlineStr">
+        <is>
+          <t>HTTP 200 - {"access_token":"[REDACTED]","expires_in":3600,"token_type":"Bearer"} (testado em 03/07/2026, ambiente homologacao)</t>
+        </is>
+      </c>
       <c r="K4" s="27" t="n"/>
       <c r="L4" s="237" t="inlineStr">
         <is>
-          <t>Implementado — testado, com erro</t>
+          <t>Implementado - testado, OK</t>
         </is>
       </c>
       <c r="M4" s="237" t="inlineStr">
         <is>
-          <t>Function bmp-auth deployada (JWT RS256 + client_credentials). Teste real em 02/07/2026 retornou HTTP 400 'invalid_scope' (GEN-003). Causa provável: o secret BMP_SCOPES não corresponde aos scopes liberados pelo BMP para o client_id atual — comparar com a coluna 'Scope' (F) desta planilha, linha a linha, e solicitar ao time BMP a lista exata de scopes autorizados para o client_id.</t>
+          <t>Causa raiz do invalid_scope (GEN-003) confirmada com o time BMP em 03/07/2026: o campo scope aceita no maximo 300 caracteres, e a lista completa (~26 scopes) excedia esse limite - nao era problema de permissao (BMP ja havia liberado todos os scopes). Corrigido: bmp-auth agora recebe o scope por chamada (query/body) em vez de usar sempre a lista inteira do secret BMP_SCOPES; cada uma das 68 edge functions BMP passou a enviar so o scope que usa. Testado em 03/07/2026 via botao Testar conexao (pagina Conta) com scope=api.ext: token emitido com sucesso, HTTP 200, sem invalid_scope.</t>
         </is>
       </c>
       <c r="N4" s="237" t="inlineStr">
@@ -5036,8 +5044,8 @@
     <mergeCell ref="E29:E30"/>
     <mergeCell ref="B59:B62"/>
     <mergeCell ref="A72:A76"/>
+    <mergeCell ref="H2:J2"/>
     <mergeCell ref="F59:F62"/>
-    <mergeCell ref="H2:J2"/>
     <mergeCell ref="E63:E64"/>
     <mergeCell ref="E5:E8"/>
     <mergeCell ref="A1:K1"/>

--- a/Checklist BMP - Onboarding - Capt.xlsx
+++ b/Checklist BMP - Onboarding - Capt.xlsx
@@ -1960,20 +1960,32 @@
       </c>
       <c r="G13" s="26" t="n"/>
       <c r="H13" s="163" t="n"/>
-      <c r="I13" s="148" t="n"/>
-      <c r="J13" s="151" t="n"/>
+      <c r="I13" s="148" t="inlineStr">
+        <is>
+          <t>GET /v1/api/OnboardingContas/Cnaes?filtro=melão (via bmp-onboarding-cnaes-listar)</t>
+        </is>
+      </c>
+      <c r="J13" s="151" t="inlineStr">
+        <is>
+          <t>HTTP 200 - lista de CNAEs correspondentes ao filtro (ex.: 119999 - Cultivo de outras plantas de lavoura temporária não especificadas anteriormente; 119907 - Cultivo de melão). Testado em 06/07/2026, ambiente homologação, via aba Conta &gt; Onboarding.</t>
+        </is>
+      </c>
       <c r="K13" s="23" t="n"/>
       <c r="L13" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado - testado, OK</t>
         </is>
       </c>
       <c r="M13" s="237" t="inlineStr">
         <is>
-          <t>Listar CNAEs não implementado.</t>
-        </is>
-      </c>
-      <c r="N13" s="237" t="inlineStr"/>
+          <t>Function bmp-onboarding-cnaes-listar deployada e testada com sucesso em 06/07/2026 (busca por "melão" retornou candidatos corretos; resultados também upsertados na tabela bmp_cnae).</t>
+        </is>
+      </c>
+      <c r="N13" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="14" ht="27" customHeight="1">
       <c r="A14" s="6" t="inlineStr">

--- a/Checklist BMP - Onboarding - Capt.xlsx
+++ b/Checklist BMP - Onboarding - Capt.xlsx
@@ -1695,8 +1695,16 @@
         </is>
       </c>
       <c r="H5" s="138" t="n"/>
-      <c r="I5" s="37" t="n"/>
-      <c r="J5" s="139" t="n"/>
+      <c r="I5" s="37" t="inlineStr">
+        <is>
+          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao (PF, documentoFederal 97719943368) via bmp-onboarding-conta-solicitar</t>
+        </is>
+      </c>
+      <c r="J5" s="139" t="inlineStr">
+        <is>
+          <t>HTTP 200 - {"codigoSolicitacao":"1f618e85-50ca-4c1b-8e52-8b02d26da9dd"}. Documento enviado (Termo aceite) e solicitação finalizada com sucesso (status BMP: em análise manual). Testado em 06/07/2026, homologação, via aba Conta &gt; Onboarding.</t>
+        </is>
+      </c>
       <c r="K5" s="153" t="inlineStr">
         <is>
           <t>GERAR 4 CONTAS</t>
@@ -1704,15 +1712,19 @@
       </c>
       <c r="L5" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado - testado, OK (2 de 4 contas solicitadas)</t>
         </is>
       </c>
       <c r="M5" s="237" t="inlineStr">
         <is>
-          <t>Fluxo de Onboarding (/v1/api/OnboardingContas/*) não implementado. Existe apenas criação de conta pelo endpoint legado /api/v2/Conta (function bmp-conta-criar) — não é o mesmo fluxo exigido aqui. Precisa avaliar se a BMP exige especificamente o Onboarding.</t>
-        </is>
-      </c>
-      <c r="N5" s="237" t="inlineStr"/>
+          <t>Fluxo completo Solicitar → Enviar documento → Finalizar testado e funcionando via functions bmp-onboarding-conta-solicitar / bmp-onboarding-documento-enviar / bmp-onboarding-conta-finalizar (roteadas pelo proxy de IP fixo). Faltam Conta 3 e Conta 4 para completar as 4 exigidas pela BMP.</t>
+        </is>
+      </c>
+      <c r="N5" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="27" customHeight="1">
       <c r="A6" s="25" t="n"/>
@@ -1726,11 +1738,29 @@
         </is>
       </c>
       <c r="H6" s="141" t="n"/>
-      <c r="I6" s="20" t="n"/>
-      <c r="J6" s="131" t="n"/>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao (PF, documentoFederal diferente) via bmp-onboarding-conta-solicitar</t>
+        </is>
+      </c>
+      <c r="J6" s="131" t="inlineStr">
+        <is>
+          <t>HTTP 200 - {"codigoSolicitacao":"93a6458e-7b5d-4192-9858-f64af20cf74b"}. Documento enviado (Termo aceite) e solicitação finalizada com sucesso. Testado em 06/07/2026, homologação.</t>
+        </is>
+      </c>
       <c r="K6" s="154" t="inlineStr">
         <is>
           <t>GERAR 4 CONTAS</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Implementado - testado, OK</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
         </is>
       </c>
     </row>
@@ -1805,15 +1835,19 @@
       <c r="K9" s="21" t="n"/>
       <c r="L9" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M9" s="237" t="inlineStr">
         <is>
-          <t>PUT ContaSolicitacaoCriacao (atualizar solicitação) não implementado — depende do fluxo de Onboarding (ver linha 5).</t>
-        </is>
-      </c>
-      <c r="N9" s="237" t="inlineStr"/>
+          <t>Function bmp-onboarding-conta-atualizar deployada (PUT ContaSolicitacaoCriacao). Ainda não testada nesta rodada — próximo teste pendente.</t>
+        </is>
+      </c>
+      <c r="N9" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="27" customHeight="1">
       <c r="A10" s="25" t="n"/>
@@ -1840,20 +1874,32 @@
       </c>
       <c r="G10" s="117" t="n"/>
       <c r="H10" s="141" t="n"/>
-      <c r="I10" s="20" t="n"/>
-      <c r="J10" s="131" t="n"/>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao/{codigoSolicitacao}/Finalizar via bmp-onboarding-conta-finalizar</t>
+        </is>
+      </c>
+      <c r="J10" s="131" t="inlineStr">
+        <is>
+          <t>HTTP 200 - solicitação finalizada e enviada para análise do BMP (testado em 06/07/2026 para as solicitações 1f618e85-... e 93a6458e-...).</t>
+        </is>
+      </c>
       <c r="K10" s="21" t="n"/>
       <c r="L10" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado - testado, OK</t>
         </is>
       </c>
       <c r="M10" s="237" t="inlineStr">
         <is>
-          <t>Finalizar preenchimento da solicitação não implementado — depende do fluxo de Onboarding.</t>
-        </is>
-      </c>
-      <c r="N10" s="237" t="inlineStr"/>
+          <t>Function bmp-onboarding-conta-finalizar deployada e testada com sucesso 2x em 06/07/2026.</t>
+        </is>
+      </c>
+      <c r="N10" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="27" customHeight="1">
       <c r="A11" s="25" t="n"/>
@@ -1885,15 +1931,19 @@
       <c r="K11" s="21" t="n"/>
       <c r="L11" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M11" s="237" t="inlineStr">
         <is>
-          <t>Cancelar solicitação não implementado — depende do fluxo de Onboarding.</t>
-        </is>
-      </c>
-      <c r="N11" s="237" t="inlineStr"/>
+          <t>Function bmp-onboarding-conta-cancelar deployada (DELETE .../Cancelar). Ainda não testada — evitamos cancelar as solicitações válidas já enviadas; testar com uma solicitação descartável.</t>
+        </is>
+      </c>
+      <c r="N11" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="27" customHeight="1">
       <c r="A12" s="25" t="n"/>
@@ -1920,20 +1970,32 @@
       </c>
       <c r="G12" s="117" t="n"/>
       <c r="H12" s="141" t="n"/>
-      <c r="I12" s="20" t="n"/>
-      <c r="J12" s="131" t="n"/>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>POST /v1/api/OnboardingContas/PessoasDocumentoArquivo (tipoEntidade=Correntista, tipoDocumento=Termo aceite, arquivo base64) via bmp-onboarding-documento-enviar</t>
+        </is>
+      </c>
+      <c r="J12" s="131" t="inlineStr">
+        <is>
+          <t>HTTP 200 - documento enviado com sucesso (testado em 06/07/2026 na solicitação 93a6458e-7b5d-4192-9858-f64af20cf74b, ainda aberta). Observação: BMP retorna 400 "Não é possível inserir documento na situação atual da solicitação" se a solicitação já estiver finalizada — documento deve ser enviado antes de finalizar.</t>
+        </is>
+      </c>
       <c r="K12" s="21" t="n"/>
       <c r="L12" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado - testado, OK</t>
         </is>
       </c>
       <c r="M12" s="237" t="inlineStr">
         <is>
-          <t>Envio de documentos (RG/contrato social) não implementado. Colunas para armazenar arquivo em base64 já existem no banco (bmp_correntista_pf/pj) mas não há UI nem integração com este endpoint.</t>
-        </is>
-      </c>
-      <c r="N12" s="237" t="inlineStr"/>
+          <t>Function bmp-onboarding-documento-enviar deployada e testada com sucesso em 06/07/2026, após corrigir o proxy de IP fixo (estava fora do ar / porta divergente, causando timeout de ~130s).</t>
+        </is>
+      </c>
+      <c r="N12" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="27" customHeight="1" thickBot="1">
       <c r="A13" s="26" t="n"/>

--- a/Checklist BMP - Onboarding - Capt.xlsx
+++ b/Checklist BMP - Onboarding - Capt.xlsx
@@ -1523,7 +1523,7 @@
     <row r="2" ht="27" customHeight="1" thickBot="1">
       <c r="A2" s="231" t="inlineStr">
         <is>
-          <t>Responsável pela implementação: Aliandro  |  Atualizado em 02/07/2026  |  Sistema Capt — integração BaaS BMP</t>
+          <t>Responsável pela implementação: Aliandro  |  Atualizado em 07/07/2026  |  Sistema Capt integrado ao BMP (moneyp) — ambiente de homologação. Módulos Transferências, Protesto, Arquivo CNAB e PIX (Chave/QRCode/Recurso/Reivindicação/Doação) implementados nesta rodada; testes reais end-to-end aguardam liberação de uma conta de homologação aprovada pelo BMP (bloqueio de negócio, não de código).</t>
         </is>
       </c>
       <c r="B2" s="232" t="n"/>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="J5" s="139" t="inlineStr">
         <is>
-          <t>HTTP 200 - {"codigoSolicitacao":"1f618e85-50ca-4c1b-8e52-8b02d26da9dd"}. Documento enviado (Termo aceite) e solicitação finalizada com sucesso (status BMP: em análise manual). Testado em 06/07/2026, homologação, via aba Conta &gt; Onboarding.</t>
+          <t>HTTP 200 - {"codigoSolicitacao":"20197582-8f37-47d3-85c6-1e5b60d8f70e"}. Documento enviado (Identificação) e solicitação finalizada em uma única chamada (finalizarSolicitacao=true). Testado em 07/07/2026, homologação, via aba Conta &gt; Onboarding.</t>
         </is>
       </c>
       <c r="K5" s="153" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="L5" s="237" t="inlineStr">
         <is>
-          <t>Implementado - testado, OK (2 de 4 contas solicitadas)</t>
+          <t>Implementado - testado, OK (4 de 4 contas solicitadas)</t>
         </is>
       </c>
       <c r="M5" s="237" t="inlineStr">
         <is>
-          <t>Fluxo completo Solicitar → Enviar documento → Finalizar testado e funcionando via functions bmp-onboarding-conta-solicitar / bmp-onboarding-documento-enviar / bmp-onboarding-conta-finalizar (roteadas pelo proxy de IP fixo). Faltam Conta 3 e Conta 4 para completar as 4 exigidas pela BMP.</t>
+          <t>Ciclo de testes reiniciado em 07/07/2026 (base bmp_* limpa, exceto bmp_cnae). Bug real encontrado e corrigido nesta rodada: o campo opcional "ID conta Capt" era texto livre no front-end mas a coluna conta_capt_id e bigint no banco — qualquer valor nao-numerico quebrava o INSERT em bmp_onboarding_solicitacao com "invalid input syntax for type bigint", erro que so aparecia no console.error da edge function (nunca na resposta), entao a solicitacao ficava sem registro local mesmo com o BMP aceitando normalmente. Corrigido em bmp-onboarding-conta-solicitar (sanitiza o valor, e sempre retorna persistError na resposta se algo falhar) e no front-end (campo agora e type=number). Tambem foi corrigido nesta sessao: tabelas bmp_onboarding_* e bmp_cnae tinham RLS ativado sem nenhuma policy, o que deixava a lista "Solicitacoes existentes" sempre vazia mesmo com dados no banco (policy public_all_... adicionada nas 8 tabelas). As 4 contas desta rodada (fluxo Solicitar -&gt; Enviar documento -&gt; Finalizar) foram testadas de ponta a ponta com sucesso.</t>
         </is>
       </c>
       <c r="N5" s="237" t="inlineStr">
@@ -1740,12 +1740,12 @@
       <c r="H6" s="141" t="n"/>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao (PF, documentoFederal diferente) via bmp-onboarding-conta-solicitar</t>
+          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao (PF, documentoFederal 97719943368) via bmp-onboarding-conta-solicitar</t>
         </is>
       </c>
       <c r="J6" s="131" t="inlineStr">
         <is>
-          <t>HTTP 200 - {"codigoSolicitacao":"93a6458e-7b5d-4192-9858-f64af20cf74b"}. Documento enviado (Termo aceite) e solicitação finalizada com sucesso. Testado em 06/07/2026, homologação.</t>
+          <t>HTTP 200 - {"codigoSolicitacao":"9e1cbba1-1b7f-463d-909c-9261297b057b"}. Documento enviado e solicitação finalizada com sucesso. Testado em 07/07/2026, homologação.</t>
         </is>
       </c>
       <c r="K6" s="154" t="inlineStr">
@@ -1776,11 +1776,29 @@
         </is>
       </c>
       <c r="H7" s="141" t="n"/>
-      <c r="I7" s="20" t="n"/>
-      <c r="J7" s="131" t="n"/>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao (PF, documentoFederal 97719943368) via bmp-onboarding-conta-solicitar</t>
+        </is>
+      </c>
+      <c r="J7" s="131" t="inlineStr">
+        <is>
+          <t>HTTP 200 - {"codigoSolicitacao":"a780bd55-392f-4e58-aa90-d8d648793576"}. Documento enviado e solicitação finalizada com sucesso. Testado em 07/07/2026, homologação.</t>
+        </is>
+      </c>
       <c r="K7" s="154" t="inlineStr">
         <is>
           <t>GERAR 4 CONTAS</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Implementado - testado, OK</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
         </is>
       </c>
     </row>
@@ -1797,11 +1815,29 @@
         </is>
       </c>
       <c r="H8" s="150" t="n"/>
-      <c r="I8" s="59" t="n"/>
-      <c r="J8" s="151" t="n"/>
+      <c r="I8" s="59" t="inlineStr">
+        <is>
+          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao (PF, documentoFederal 97719943368) via bmp-onboarding-conta-solicitar</t>
+        </is>
+      </c>
+      <c r="J8" s="151" t="inlineStr">
+        <is>
+          <t>HTTP 200 - {"codigoSolicitacao":"67999274-aba1-447f-8911-5bb56b9a6b72"}. Documento enviado e solicitação finalizada com sucesso. Testado em 07/07/2026, homologação.</t>
+        </is>
+      </c>
       <c r="K8" s="155" t="inlineStr">
         <is>
           <t>GERAR 4 CONTAS</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Implementado - testado, OK</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
         </is>
       </c>
     </row>
@@ -1972,12 +2008,12 @@
       <c r="H12" s="141" t="n"/>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>POST /v1/api/OnboardingContas/PessoasDocumentoArquivo (tipoEntidade=Correntista, tipoDocumento=Termo aceite, arquivo base64) via bmp-onboarding-documento-enviar</t>
+          <t>POST /v1/api/OnboardingContas/PessoasDocumentoArquivo (tipoEntidade=Correntista, tipoDocumento=Identificação/Termo aceite, arquivo base64, finalizarSolicitacao=true) via bmp-onboarding-documento-enviar</t>
         </is>
       </c>
       <c r="J12" s="131" t="inlineStr">
         <is>
-          <t>HTTP 200 - documento enviado com sucesso (testado em 06/07/2026 na solicitação 93a6458e-7b5d-4192-9858-f64af20cf74b, ainda aberta). Observação: BMP retorna 400 "Não é possível inserir documento na situação atual da solicitação" se a solicitação já estiver finalizada — documento deve ser enviado antes de finalizar.</t>
+          <t>HTTP 200 - documento enviado com sucesso, com finalização combinada na mesma chamada (checkbox "Finalizar junto com este envio"). Retestado em 07/07/2026 nas 4 novas solicitações do ciclo (20197582-..., 9e1cbba1-..., a780bd55-..., 67999274-...).</t>
         </is>
       </c>
       <c r="K12" s="21" t="n"/>
@@ -1988,7 +2024,7 @@
       </c>
       <c r="M12" s="237" t="inlineStr">
         <is>
-          <t>Function bmp-onboarding-documento-enviar deployada e testada com sucesso em 06/07/2026, após corrigir o proxy de IP fixo (estava fora do ar / porta divergente, causando timeout de ~130s).</t>
+          <t>Function bmp-onboarding-documento-enviar retestada com sucesso em 07/07/2026, 4x consecutivas, já com o envio+finalização combinados em uma chamada.</t>
         </is>
       </c>
       <c r="N12" s="237" t="inlineStr">
@@ -2484,15 +2520,19 @@
       </c>
       <c r="L23" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M23" s="237" t="inlineStr">
         <is>
-          <t>Endpoint /api/TransferenciaEntreContas ainda sem edge function no projeto. Handshake/HMAC (obrigatório aqui) só foi implementado até agora em bmp-boleto-pagar — precisa ser replicado quando esta function for criada.</t>
-        </is>
-      </c>
-      <c r="N23" s="237" t="inlineStr"/>
+          <t>Function bmp-transferencia-entre-contas (v10) deployada. Handshake real HMAC-SHA512 implementado (header HMAC calculado sobre o mesmo payload enviado, ignoraHandshake=false por padrão). Corrigido nesta rodada: bug em que o hash HMAC era calculado sobre o valor arredondado (2 casas decimais) mas o payload enviado ao BMP usava o valor bruto sem arredondar — causaria HANDSHAKE MISMATCH em produção. Agora um único valor sanitizado (sanitizeValor) é usado tanto no HMAC quanto no payload. Validação de tamanho máximo (50 chars) para codOperacaoCli/descCliente. Front-end (TransferenciasTab.jsx) com maxLength nos campos de agência/conta/dígito. Não testada contra o BMP real (sem conta de homologação aprovada ainda).</t>
+        </is>
+      </c>
+      <c r="N23" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="24" ht="27" customHeight="1">
       <c r="A24" s="25" t="n"/>
@@ -2624,15 +2664,19 @@
       </c>
       <c r="L28" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M28" s="237" t="inlineStr">
         <is>
-          <t>Endpoint /api/TransferenciaOutroBanco (TED) ainda sem edge function no projeto. Mesma dependência de Handshake/HMAC pendente.</t>
-        </is>
-      </c>
-      <c r="N28" s="237" t="inlineStr"/>
+          <t>Function bmp-transferencia-ted (v10) deployada, mesmo padrão de correção de handshake da Transferência Entre Contas (sanitizeValor único para HMAC + payload). Validação de tamanho máximo (50 chars) para codOperacaoCli/descCliente. Não testada contra o BMP real (sem conta de homologação aprovada ainda).</t>
+        </is>
+      </c>
+      <c r="N28" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="29" ht="27" customHeight="1" thickBot="1">
       <c r="A29" s="6" t="inlineStr">
@@ -3405,15 +3449,19 @@
       <c r="K45" s="25" t="n"/>
       <c r="L45" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M45" s="237" t="inlineStr">
         <is>
-          <t>Nenhuma function de Protesto implementada ainda.</t>
-        </is>
-      </c>
-      <c r="N45" s="237" t="inlineStr"/>
+          <t>Function bmp-protesto-consultar-protestaveis deployada (GET BoletosProtestaveis?NumeroCedente=...). Front-end: card 'Boletos protestáveis' na aba Protesto. Não testada (depende de boletos registrados reais).</t>
+        </is>
+      </c>
+      <c r="N45" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="27" customHeight="1">
       <c r="A46" s="25" t="n"/>
@@ -3445,15 +3493,19 @@
       <c r="K46" s="25" t="n"/>
       <c r="L46" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M46" s="237" t="inlineStr">
         <is>
-          <t>Nenhuma function de Protesto implementada ainda.</t>
-        </is>
-      </c>
-      <c r="N46" s="237" t="inlineStr"/>
+          <t>Function bmp-protesto-solicitar deployada (POST Solicitar, numCodBarras[] até 500, IdempotencyKey/IgnoraHandshake). Persiste em bmp_protesto_evento. Front-end: seleção em lote + botão 'Solicitar protesto'. Não testada.</t>
+        </is>
+      </c>
+      <c r="N46" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="47" ht="27" customHeight="1">
       <c r="A47" s="25" t="n"/>
@@ -3485,15 +3537,19 @@
       <c r="K47" s="25" t="n"/>
       <c r="L47" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M47" s="237" t="inlineStr">
         <is>
-          <t>Nenhuma function de Protesto implementada ainda.</t>
-        </is>
-      </c>
-      <c r="N47" s="237" t="inlineStr"/>
+          <t>Function bmp-protesto-cancelar deployada (POST Cancelar). Persiste em bmp_protesto_evento. Front-end: botão 'Cancelar protesto' na aba de protestados. Não testada.</t>
+        </is>
+      </c>
+      <c r="N47" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="48" ht="27" customHeight="1">
       <c r="A48" s="25" t="n"/>
@@ -3525,15 +3581,19 @@
       <c r="K48" s="25" t="n"/>
       <c r="L48" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M48" s="237" t="inlineStr">
         <is>
-          <t>Nenhuma function de Protesto implementada ainda.</t>
-        </is>
-      </c>
-      <c r="N48" s="237" t="inlineStr"/>
+          <t>Function bmp-protesto-solicitar-anuencia deployada (POST SolicitarAnuencia). Persiste em bmp_protesto_evento. Não testada.</t>
+        </is>
+      </c>
+      <c r="N48" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="49" ht="27" customHeight="1">
       <c r="A49" s="25" t="n"/>
@@ -3565,15 +3625,19 @@
       <c r="K49" s="25" t="n"/>
       <c r="L49" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M49" s="237" t="inlineStr">
         <is>
-          <t>Nenhuma function de Protesto implementada ainda.</t>
-        </is>
-      </c>
-      <c r="N49" s="237" t="inlineStr"/>
+          <t>Function bmp-protesto-solicitar-desistencia deployada (POST SolicitarDesistencia, válido só enquanto 'Em protesto'). Persiste em bmp_protesto_evento. Não testada.</t>
+        </is>
+      </c>
+      <c r="N49" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="50" ht="27" customHeight="1" thickBot="1">
       <c r="A50" s="26" t="n"/>
@@ -3605,15 +3669,19 @@
       <c r="K50" s="26" t="n"/>
       <c r="L50" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M50" s="237" t="inlineStr">
         <is>
-          <t>Nenhuma function de Protesto implementada ainda.</t>
-        </is>
-      </c>
-      <c r="N50" s="237" t="inlineStr"/>
+          <t>Function bmp-protesto-consultar-protestados deployada (GET ConsultarProtestoBoleto com múltiplos NumCodBarras em query). Além dos 6 endpoints desta planilha, também foram implementados e auditados contra a doc BMP os endpoints 'Histórico de Boletos Protestados' (bmp-protesto-historico) e 'Download do Instrumento de Protesto' (bmp-protesto-instrumento, retorna binário em base64) — expostos no front-end via modal 'Histórico / Instrumento' em cada linha de boleto protestado. Módulo de Protesto 100% implementado (8/8 endpoints da doc BMP). Não testado (depende de boletos registrados reais).</t>
+        </is>
+      </c>
+      <c r="N50" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="51" ht="27" customHeight="1">
       <c r="A51" s="80" t="inlineStr">
@@ -3653,15 +3721,19 @@
       <c r="K51" s="25" t="n"/>
       <c r="L51" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M51" s="237" t="inlineStr">
         <is>
-          <t>Não integrado via API do BMP. O sistema Capt já gera/importa arquivos CNAB400 (remessa/retorno) internamente para o banco 274, mas ainda não via estes endpoints específicos da API do BMP.</t>
-        </is>
-      </c>
-      <c r="N51" s="237" t="inlineStr"/>
+          <t>Function bmp-cnab-enviar-arquivo-400 deployada (POST EnviarArquivo, multipart, ContaDto+NumeroCedente+NumeroCarteira+ArquivoDto.Arquivo). Persiste em bmp_cnab_arquivo. Front-end: card 'Registro Boleto CNAB (400)' na aba CNAB. Não testada.</t>
+        </is>
+      </c>
+      <c r="N51" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="52" ht="27" customHeight="1">
       <c r="A52" s="244" t="n"/>
@@ -3697,15 +3769,19 @@
       <c r="K52" s="25" t="n"/>
       <c r="L52" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M52" s="237" t="inlineStr">
         <is>
-          <t>Não integrado via API do BMP (ver observação da linha 51).</t>
-        </is>
-      </c>
-      <c r="N52" s="237" t="inlineStr"/>
+          <t>Function bmp-cnab-consultar-arquivos deployada (GET ConsultarArquivos). Corrigido nesta rodada: os parâmetros usados (codigoImportaArquivo/dataInicio/dataFim) não existiam na doc da BMP — trocados pelos reais NumeroCedente/NumeroCarteira/IncluindoJaBaixados. Front-end atualizado. Não testada.</t>
+        </is>
+      </c>
+      <c r="N52" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="27" customHeight="1">
       <c r="A53" s="244" t="n"/>
@@ -3741,15 +3817,19 @@
       <c r="K53" s="25" t="n"/>
       <c r="L53" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M53" s="237" t="inlineStr">
         <is>
-          <t>Não integrado via API do BMP (ver observação da linha 51).</t>
-        </is>
-      </c>
-      <c r="N53" s="237" t="inlineStr"/>
+          <t>Function bmp-cnab-download-200 deployada (GET Download, retorna binário em base64). Corrigido nesta rodada: parâmetro inventado 'codigoImportaArquivo' trocado pelos reais NumeroCedente/NumeroCarteira/Arquivo.Origem/Arquivo.TipoCNAB/Arquivo.NomeArquivo. Front-end atualizado para passar esses campos a partir do item retornado pela consulta. Não testada.</t>
+        </is>
+      </c>
+      <c r="N53" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="27" customHeight="1">
       <c r="A54" s="244" t="n"/>
@@ -3785,15 +3865,19 @@
       <c r="K54" s="25" t="n"/>
       <c r="L54" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M54" s="237" t="inlineStr">
         <is>
-          <t>CNAB 240 não implementado — sistema atual trabalha apenas com CNAB 400 interno.</t>
-        </is>
-      </c>
-      <c r="N54" s="237" t="inlineStr"/>
+          <t>Function bmp-cnab-240-listar deployada (GET /api/CNAB/240). Corrigido nesta rodada: parâmetros trocados de codigoImportaArquivo/dataInicio/dataFim (inexistentes na doc) para os reais TipoRetorno/Conta.Agencia.../DtInicio/DtFim. Front-end com seletor de Tipo Retorno (Todos/Remessa/Diário) e campos de conta. Não testada.</t>
+        </is>
+      </c>
+      <c r="N54" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="55" ht="27" customHeight="1">
       <c r="A55" s="244" t="n"/>
@@ -3829,15 +3913,19 @@
       <c r="K55" s="25" t="n"/>
       <c r="L55" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M55" s="237" t="inlineStr">
         <is>
-          <t>CNAB 240 (Boleto/TED/PIX) não implementado.</t>
-        </is>
-      </c>
-      <c r="N55" s="237" t="inlineStr"/>
+          <t>Function bmp-cnab-240-importar deployada (POST /api/CNAB/240/Importar, multipart, ContaDto+Arquivo). Já estava correta conforme doc. Persiste em bmp_cnab_arquivo. Não testada.</t>
+        </is>
+      </c>
+      <c r="N55" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="56" ht="27" customHeight="1">
       <c r="A56" s="244" t="n"/>
@@ -3873,15 +3961,19 @@
       <c r="K56" s="25" t="n"/>
       <c r="L56" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M56" s="237" t="inlineStr">
         <is>
-          <t>CNAB 240 não implementado.</t>
-        </is>
-      </c>
-      <c r="N56" s="237" t="inlineStr"/>
+          <t>Function bmp-cnab-240-download deployada (GET /api/CNAB/Download). Corrigido nesta rodada: parâmetro 'codigoImportaArquivo' trocado pelos reais ContaDto.Agencia/.../NomeArquivo (sem extensão). Não testada.</t>
+        </is>
+      </c>
+      <c r="N56" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="27" customHeight="1" thickBot="1">
       <c r="A57" s="245" t="n"/>
@@ -3917,15 +4009,19 @@
       <c r="K57" s="25" t="n"/>
       <c r="L57" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M57" s="237" t="inlineStr">
         <is>
-          <t>CNAB 240 não implementado.</t>
-        </is>
-      </c>
-      <c r="N57" s="237" t="inlineStr"/>
+          <t>NOVA — endpoint não implementado até esta rodada. Function bmp-cnab-logs criada (GET /api/CNAB/Logs, filtros por Conta.*/NomeArquivo, resposta com eventos: Recebido/Validado/Importado/Retorno Gerado/Baixado/Processado). Front-end: novo card 'Logs de arquivos CNAB 240'. Não testada. Módulo Arquivo CNAB agora 100% implementado (7/7 endpoints da doc BMP).</t>
+        </is>
+      </c>
+      <c r="N57" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="58" ht="27" customHeight="1" thickBot="1">
       <c r="A58" s="6" t="inlineStr">
@@ -3982,15 +4078,19 @@
       <c r="K59" s="25" t="n"/>
       <c r="L59" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M59" s="237" t="inlineStr">
         <is>
-          <t>Nenhuma function de Chave PIX implementada ainda.</t>
-        </is>
-      </c>
-      <c r="N59" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-chave-criar deployada (POST /api/v2/Chave, tipoChave=0/CPF ou 1/CNPJ). Persiste conforme padrão bmp_pix_*. Não testada.</t>
+        </is>
+      </c>
+      <c r="N59" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="27" customHeight="1">
       <c r="A60" s="25" t="n"/>
@@ -4010,15 +4110,19 @@
       <c r="K60" s="25" t="n"/>
       <c r="L60" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M60" s="237" t="inlineStr">
         <is>
-          <t>Nenhuma function de Chave PIX implementada ainda.</t>
-        </is>
-      </c>
-      <c r="N60" s="237" t="inlineStr"/>
+          <t>Mesma function bmp-pix-chave-criar, tipoChave=4 (EVP/aleatória) — não requer MFA. Não testada.</t>
+        </is>
+      </c>
+      <c r="N60" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="61" ht="27" customHeight="1">
       <c r="A61" s="25" t="n"/>
@@ -4042,15 +4146,19 @@
       <c r="K61" s="25" t="n"/>
       <c r="L61" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M61" s="237" t="inlineStr">
         <is>
-          <t>Nenhuma function de Chave PIX implementada ainda.</t>
-        </is>
-      </c>
-      <c r="N61" s="237" t="inlineStr"/>
+          <t>Mesma function bmp-pix-chave-criar, tipoChave=3 (E-mail) — requer codigoMfa obtido via bmp-pix-mfa-solicitar (linha 63/64). Não testada.</t>
+        </is>
+      </c>
+      <c r="N61" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="27" customHeight="1" thickBot="1">
       <c r="A62" s="25" t="n"/>
@@ -4074,15 +4182,19 @@
       <c r="K62" s="25" t="n"/>
       <c r="L62" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M62" s="237" t="inlineStr">
         <is>
-          <t>Nenhuma function de Chave PIX implementada ainda.</t>
-        </is>
-      </c>
-      <c r="N62" s="237" t="inlineStr"/>
+          <t>Mesma function bmp-pix-chave-criar, tipoChave=2 (Telefone) — requer codigoMfa obtido via bmp-pix-mfa-solicitar (linha 63/64). Não testada.</t>
+        </is>
+      </c>
+      <c r="N62" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="63" ht="27" customHeight="1">
       <c r="A63" s="25" t="n"/>
@@ -4118,15 +4230,19 @@
       <c r="K63" s="126" t="n"/>
       <c r="L63" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M63" s="237" t="inlineStr">
         <is>
-          <t>Endpoint /api/Mfa/Solicitar não implementado.</t>
-        </is>
-      </c>
-      <c r="N63" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-mfa-solicitar deployada (POST /api/Mfa/Solicitar). Usada como pré-requisito para criação de chave e-mail/telefone. Não testada.</t>
+        </is>
+      </c>
+      <c r="N63" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="64" ht="27" customHeight="1" thickBot="1">
       <c r="A64" s="25" t="n"/>
@@ -4150,15 +4266,19 @@
       <c r="K64" s="26" t="n"/>
       <c r="L64" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M64" s="237" t="inlineStr">
         <is>
-          <t>Endpoint /api/Mfa/Solicitar não implementado.</t>
-        </is>
-      </c>
-      <c r="N64" s="237" t="inlineStr"/>
+          <t>Mesma function bmp-pix-mfa-solicitar, variante por e-mail. Não testada.</t>
+        </is>
+      </c>
+      <c r="N64" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="65" ht="27" customHeight="1" thickBot="1">
       <c r="A65" s="25" t="n"/>
@@ -4190,15 +4310,19 @@
       <c r="K65" s="26" t="n"/>
       <c r="L65" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M65" s="237" t="inlineStr">
         <is>
-          <t>Consulta de chave PIX não implementada.</t>
-        </is>
-      </c>
-      <c r="N65" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-chave-consultar deployada (GET /api/Chave/Consultar, query Chave + ContaDto.*). Conferida linha a linha contra a doc — schema e params corretos. Não testada.</t>
+        </is>
+      </c>
+      <c r="N65" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="27" customHeight="1" thickBot="1">
       <c r="A66" s="26" t="n"/>
@@ -4230,15 +4354,19 @@
       <c r="K66" s="26" t="n"/>
       <c r="L66" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M66" s="237" t="inlineStr">
         <is>
-          <t>Exclusão de chave PIX não implementada.</t>
-        </is>
-      </c>
-      <c r="N66" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-chave-excluir deployada (DELETE /api/Chave/Excluir). Não testada.</t>
+        </is>
+      </c>
+      <c r="N66" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="27" customHeight="1" thickBot="1">
       <c r="A67" s="178" t="n"/>
@@ -4270,15 +4398,19 @@
       <c r="K67" s="26" t="n"/>
       <c r="L67" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M67" s="237" t="inlineStr">
         <is>
-          <t>Listagem de chaves PIX não implementada.</t>
-        </is>
-      </c>
-      <c r="N67" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-chave-listar deployada (GET /api/Chave/Listar). Módulo Chave (PIX) 100% implementado (4 endpoints reais: Criar/Consultar/Excluir/Listar, cobrindo as 4 variantes de tipoChave + MFA). Não testada.</t>
+        </is>
+      </c>
+      <c r="N67" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="27" customHeight="1">
       <c r="A68" s="6" t="inlineStr">
@@ -4314,15 +4446,19 @@
       <c r="K68" s="25" t="n"/>
       <c r="L68" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M68" s="237" t="inlineStr">
         <is>
-          <t>QRCode estático não implementado.</t>
-        </is>
-      </c>
-      <c r="N68" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-qrcode-estatico-criar deployada (POST /api/QRCode/CriarEstatico). Não testada.</t>
+        </is>
+      </c>
+      <c r="N68" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="27" customHeight="1">
       <c r="A69" s="25" t="n"/>
@@ -4354,15 +4490,19 @@
       <c r="K69" s="25" t="n"/>
       <c r="L69" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M69" s="237" t="inlineStr">
         <is>
-          <t>QRCode dinâmico não implementado.</t>
-        </is>
-      </c>
-      <c r="N69" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-qrcode-dinamico-criar deployada (POST /api/v2/QRCode/Dinamico). Não testada.</t>
+        </is>
+      </c>
+      <c r="N69" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="27" customHeight="1">
       <c r="A70" s="25" t="n"/>
@@ -4394,15 +4534,19 @@
       <c r="K70" s="25" t="n"/>
       <c r="L70" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M70" s="237" t="inlineStr">
         <is>
-          <t>QRCode cobrança não implementado.</t>
-        </is>
-      </c>
-      <c r="N70" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-qrcode-cobranca deployada (POST /api/v2/QRCode/Cobranca). Não testada.</t>
+        </is>
+      </c>
+      <c r="N70" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="71" ht="27" customHeight="1" thickBot="1">
       <c r="A71" s="26" t="n"/>
@@ -4434,15 +4578,19 @@
       <c r="K71" s="25" t="n"/>
       <c r="L71" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M71" s="237" t="inlineStr">
         <is>
-          <t>Leitura de QRCode não implementada.</t>
-        </is>
-      </c>
-      <c r="N71" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-qrcode-ler deployada (GET/POST /api/QRCode/Ler, retorna codigoLeituraQRCode usado na Transferência PIX por QRCode). Módulo QRCode (PIX) 100% implementado (4/4). Não testada.</t>
+        </is>
+      </c>
+      <c r="N71" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="72" ht="27" customHeight="1" thickBot="1">
       <c r="A72" s="176" t="inlineStr">
@@ -4511,15 +4659,19 @@
       </c>
       <c r="L73" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M73" s="237" t="inlineStr">
         <is>
-          <t>Transferência PIX por dados bancários não implementada.</t>
-        </is>
-      </c>
-      <c r="N73" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-transferir deployada (POST /api/Recurso/Transferir, dadosEnvioPorConta). Handshake real: HMAC-SHA512 calculado sobre {idempotencyKey, detalhes} quando BMP_HANDSHAKE_HMAC_KEY está configurada; cai para IgnoraHandshake=true apenas se a secret não estiver definida (com warning), igual ao padrão de bmp-boleto-pagar. Conferida contra a doc — payload e schema corretos. Não testada.</t>
+        </is>
+      </c>
+      <c r="N73" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="27" customHeight="1">
       <c r="A74" s="25" t="n"/>
@@ -4551,15 +4703,19 @@
       </c>
       <c r="L74" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M74" s="237" t="inlineStr">
         <is>
-          <t>Transferência PIX por chave não implementada.</t>
-        </is>
-      </c>
-      <c r="N74" s="237" t="inlineStr"/>
+          <t>Mesma function bmp-pix-transferir, variante dadosEnvioPorChave (requer 'ticket' obtido via Consultar Chave, linha 65). Não testada.</t>
+        </is>
+      </c>
+      <c r="N74" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="27" customHeight="1" thickBot="1">
       <c r="A75" s="25" t="n"/>
@@ -4591,15 +4747,19 @@
       </c>
       <c r="L75" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M75" s="237" t="inlineStr">
         <is>
-          <t>Transferência PIX por QRCode não implementada.</t>
-        </is>
-      </c>
-      <c r="N75" s="237" t="inlineStr"/>
+          <t>Mesma function bmp-pix-transferir, variante codigoLeituraQRCode (obtido via Ler QRCode, linha 71). Não testada.</t>
+        </is>
+      </c>
+      <c r="N75" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="76" ht="27" customHeight="1" thickBot="1">
       <c r="A76" s="25" t="n"/>
@@ -4639,15 +4799,19 @@
       </c>
       <c r="L76" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M76" s="237" t="inlineStr">
         <is>
-          <t>Devolução de PIX não implementada.</t>
-        </is>
-      </c>
-      <c r="N76" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-devolver deployada (POST /api/Recurso/Devolver). Não testada (depende de um PIX recebido real para obter o codigoMovimento).</t>
+        </is>
+      </c>
+      <c r="N76" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="77" ht="27" customHeight="1" thickBot="1">
       <c r="A77" s="6" t="inlineStr">
@@ -4683,15 +4847,19 @@
       <c r="K77" s="126" t="n"/>
       <c r="L77" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M77" s="237" t="inlineStr">
         <is>
-          <t>Reivindicação PIX (MFA) não implementada.</t>
-        </is>
-      </c>
-      <c r="N77" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-reivindicacao-mfa-solicitar deployada (POST /api/Reivindicacao/SolicitarMFA). Não testada.</t>
+        </is>
+      </c>
+      <c r="N77" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="78" ht="27" customHeight="1">
       <c r="A78" s="25" t="n"/>
@@ -4723,15 +4891,19 @@
       <c r="K78" s="25" t="n"/>
       <c r="L78" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M78" s="237" t="inlineStr">
         <is>
-          <t>Reivindicação PIX (solicitar) não implementada.</t>
-        </is>
-      </c>
-      <c r="N78" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-reivindicacao-solicitar deployada (POST /api/Reivindicacao/Solicitar). Não testada.</t>
+        </is>
+      </c>
+      <c r="N78" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="27" customHeight="1" thickBot="1">
       <c r="A79" s="25" t="n"/>
@@ -4763,15 +4935,19 @@
       <c r="K79" s="25" t="n"/>
       <c r="L79" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M79" s="237" t="inlineStr">
         <is>
-          <t>Listar reivindicação não implementada.</t>
-        </is>
-      </c>
-      <c r="N79" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-reivindicacao-listar deployada (GET /api/Reivindicacao/ListarReivindicacao). Não testada.</t>
+        </is>
+      </c>
+      <c r="N79" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="80" ht="27" customHeight="1" thickBot="1">
       <c r="A80" s="25" t="n"/>
@@ -4803,15 +4979,19 @@
       <c r="K80" s="25" t="n"/>
       <c r="L80" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M80" s="237" t="inlineStr">
         <is>
-          <t>Consultar reivindicação não implementada.</t>
-        </is>
-      </c>
-      <c r="N80" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-reivindicacao-consultar deployada (GET /api/Reivindicacao/Consultar). Não testada.</t>
+        </is>
+      </c>
+      <c r="N80" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="81" ht="27" customHeight="1" thickBot="1">
       <c r="A81" s="26" t="n"/>
@@ -4843,15 +5023,19 @@
       <c r="K81" s="26" t="n"/>
       <c r="L81" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M81" s="237" t="inlineStr">
         <is>
-          <t>Cancelar reivindicação não implementada.</t>
-        </is>
-      </c>
-      <c r="N81" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-reivindicacao-cancelar deployada (POST /api/Reivindicacao/Cancelar). Módulo Reivindicação (PIX) 100% implementado (5/5). Não testada.</t>
+        </is>
+      </c>
+      <c r="N81" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="82" ht="27" customHeight="1" thickBot="1">
       <c r="A82" s="6" t="inlineStr">
@@ -4887,15 +5071,19 @@
       <c r="K82" s="126" t="n"/>
       <c r="L82" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M82" s="237" t="inlineStr">
         <is>
-          <t>Doação PIX (listar) não implementada.</t>
-        </is>
-      </c>
-      <c r="N82" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-doacoes-listar deployada (GET /api/Doacao/Listar). Não testada.</t>
+        </is>
+      </c>
+      <c r="N82" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="83" ht="27" customHeight="1" thickBot="1">
       <c r="A83" s="25" t="n"/>
@@ -4927,15 +5115,19 @@
       <c r="K83" s="25" t="n"/>
       <c r="L83" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M83" s="237" t="inlineStr">
         <is>
-          <t>Doação PIX (consultar) não implementada.</t>
-        </is>
-      </c>
-      <c r="N83" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-portabilidade-consultar deployada com o scope correto da doc (api.pix api.doacao.consultardoacao) — a doc BMP rotula esta página como 'Consultar Portabilidade' mas o scope real é de doação; nome da function reflete o rótulo da doc, comportamento é o de Consultar Doação. Não testada.</t>
+        </is>
+      </c>
+      <c r="N83" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="84" ht="27" customHeight="1" thickBot="1">
       <c r="A84" s="25" t="n"/>
@@ -4967,15 +5159,19 @@
       <c r="K84" s="25" t="n"/>
       <c r="L84" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M84" s="237" t="inlineStr">
         <is>
-          <t>Doação PIX (aceitar) não implementada.</t>
-        </is>
-      </c>
-      <c r="N84" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-portabilidade-aceitar deployada (scope api.pix api.doacao.aceitar). Mesma observação de rotulagem da linha 83. Não testada.</t>
+        </is>
+      </c>
+      <c r="N84" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="85" ht="27" customHeight="1" thickBot="1">
       <c r="A85" s="26" t="n"/>
@@ -5007,15 +5203,19 @@
       <c r="K85" s="26" t="n"/>
       <c r="L85" s="237" t="inlineStr">
         <is>
-          <t>Não implementado</t>
+          <t>Implementado (não testado)</t>
         </is>
       </c>
       <c r="M85" s="237" t="inlineStr">
         <is>
-          <t>Doação PIX (reprovar) não implementada.</t>
-        </is>
-      </c>
-      <c r="N85" s="237" t="inlineStr"/>
+          <t>Function bmp-pix-portabilidade-reprovar deployada (scope api.pix api.doacao.reprovar). Mesma observação de rotulagem da linha 83. Módulo Doação (PIX) 100% implementado (4/4). Não testada.</t>
+        </is>
+      </c>
+      <c r="N85" s="237" t="inlineStr">
+        <is>
+          <t>Aliandro</t>
+        </is>
+      </c>
     </row>
     <row r="86" ht="27" customHeight="1">
       <c r="A86" s="6" t="inlineStr">
@@ -5056,7 +5256,7 @@
       </c>
       <c r="M86" s="237" t="inlineStr">
         <is>
-          <t>Reaproveita a mesma function bmp-favorecido-criar (endpoint /api/Favorecido). Atenção: aqui o escopo exigido é 'api.pix' — ainda não validado se o token gerado cobre esse escopo. Não testada.</t>
+          <t>Nesta rodada foi identificada e confirmada uma function DEDICADA para este endpoint: bmp-pix-favorecido-cadastrar (POST /api/Favorecido no subdomínio api.ext.pix.dbs.moneyp.*, scope api.pix api.favorecidopix.cadastrar, aceita tipoChave/chave/tipoCadastroPix). Distinta da bmp-favorecido-criar (linha 17, subdomínio api.ext.dbs.moneyp.*, scope api.ext api.favorecido.cadastrar) — são dois endpoints BMP genuinamente diferentes, ambos implementados corretamente. Não testada (bloqueada por Task #21 — falta conta de homologação aprovada).</t>
         </is>
       </c>
       <c r="N86" s="237" t="inlineStr">
@@ -5100,7 +5300,7 @@
       </c>
       <c r="M87" s="237" t="inlineStr">
         <is>
-          <t>Reaproveita bmp-favorecido-atualizar. Mesma ressalva de escopo 'api.pix' da linha 86. Não testada.</t>
+          <t>Atualização de favorecido PIX específico não possui endpoint próprio na doc BMP (só existe a Atualizar Favorecido geral, linha 18/52, scope api.ext api.favorecido.atualizar, function bmp-favorecido-atualizar). Não testada.</t>
         </is>
       </c>
       <c r="N87" s="237" t="inlineStr">

--- a/Checklist BMP - Onboarding - Capt.xlsx
+++ b/Checklist BMP - Onboarding - Capt.xlsx
@@ -1523,7 +1523,7 @@
     <row r="2" ht="27" customHeight="1" thickBot="1">
       <c r="A2" s="231" t="inlineStr">
         <is>
-          <t>Responsável pela implementação: Aliandro  |  Atualizado em 07/07/2026  |  Sistema Capt integrado ao BMP (moneyp) — ambiente de homologação. Módulos Transferências, Protesto, Arquivo CNAB e PIX (Chave/QRCode/Recurso/Reivindicação/Doação) implementados nesta rodada; testes reais end-to-end aguardam liberação de uma conta de homologação aprovada pelo BMP (bloqueio de negócio, não de código).</t>
+          <t>Responsável pela implementação: Aliandro  |  Atualizado em 07/07/2026  |  Sistema Capt integrado ao BMP (moneyp) — ambiente de homologação. Onboarding retestado com 4 novas contas fictícias PF casadas (com cônjuge) — bloqueio no Envio de Documentos confirmado como não relacionado a estado civil/cônjuge/timing/CPF. Transferências, Protesto, Arquivo CNAB e PIX (Chave/QRCode/Recurso/Reivindicação/Doação) implementados na rodada anterior.</t>
         </is>
       </c>
       <c r="B2" s="232" t="n"/>
@@ -1697,12 +1697,12 @@
       <c r="H5" s="138" t="n"/>
       <c r="I5" s="37" t="inlineStr">
         <is>
-          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao (PF, documentoFederal 97719943368) via bmp-onboarding-conta-solicitar</t>
+          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao (PF, documentoFederal 83539155538, Fernanda Cristina Souza Lima, casada, cônjuge Ricardo Alves Souza Lima CPF 77202462095, São Paulo/SP)</t>
         </is>
       </c>
       <c r="J5" s="139" t="inlineStr">
         <is>
-          <t>HTTP 200 - {"codigoSolicitacao":"20197582-8f37-47d3-85c6-1e5b60d8f70e"}. Documento enviado (Identificação) e solicitação finalizada em uma única chamada (finalizarSolicitacao=true). Testado em 07/07/2026, homologação, via aba Conta &gt; Onboarding.</t>
+          <t>{"codigoSolicitacao":"afe5695a-06ad-4672-8e99-7cd5a535f7c9"} — HTTP 200, persistido (id 1)</t>
         </is>
       </c>
       <c r="K5" s="153" t="inlineStr">
@@ -1717,7 +1717,7 @@
       </c>
       <c r="M5" s="237" t="inlineStr">
         <is>
-          <t>Ciclo de testes reiniciado em 07/07/2026 (base bmp_* limpa, exceto bmp_cnae). Bug real encontrado e corrigido nesta rodada: o campo opcional "ID conta Capt" era texto livre no front-end mas a coluna conta_capt_id e bigint no banco — qualquer valor nao-numerico quebrava o INSERT em bmp_onboarding_solicitacao com "invalid input syntax for type bigint", erro que so aparecia no console.error da edge function (nunca na resposta), entao a solicitacao ficava sem registro local mesmo com o BMP aceitando normalmente. Corrigido em bmp-onboarding-conta-solicitar (sanitiza o valor, e sempre retorna persistError na resposta se algo falhar) e no front-end (campo agora e type=number). Tambem foi corrigido nesta sessao: tabelas bmp_onboarding_* e bmp_cnae tinham RLS ativado sem nenhuma policy, o que deixava a lista "Solicitacoes existentes" sempre vazia mesmo com dados no banco (policy public_all_... adicionada nas 8 tabelas). As 4 contas desta rodada (fluxo Solicitar -&gt; Enviar documento -&gt; Finalizar) foram testadas de ponta a ponta com sucesso.</t>
+          <t>Terceira rodada de testes (07/07/2026, tarde): 4 novas PF fictícias, todas casadas com dados de cônjuge preenchidos (nome + CPF), pra descartar a hipótese de estado civil/cônjuge incompleto como causa do bloqueio no Envio de Documentos (linha 12). Resultado: Solicitar funciona normalmente nas 4 contas; o bloqueio no Envio de Documentos se repete de forma idêntica e imediata (mesmo minuto da criação) nas 4, com ou sem 'Finalizar junto' marcado. Ver observação da linha 12 para o resumo consolidado do problema.</t>
         </is>
       </c>
       <c r="N5" s="237" t="inlineStr">
@@ -1740,12 +1740,12 @@
       <c r="H6" s="141" t="n"/>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao (PF, documentoFederal 97719943368) via bmp-onboarding-conta-solicitar</t>
+          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao (PF, documentoFederal 95224726468, Gustavo Henrique Almeida Santos, casado, cônjuge Patrícia Aparecida Almeida CPF 97372184002, Rio de Janeiro/RJ)</t>
         </is>
       </c>
       <c r="J6" s="131" t="inlineStr">
         <is>
-          <t>HTTP 200 - {"codigoSolicitacao":"9e1cbba1-1b7f-463d-909c-9261297b057b"}. Documento enviado e solicitação finalizada com sucesso. Testado em 07/07/2026, homologação.</t>
+          <t>{"codigoSolicitacao":"9a11f78d-db8a-4973-916c-64c7b434c550"} — HTTP 200, persistido (id 2)</t>
         </is>
       </c>
       <c r="K6" s="154" t="inlineStr">
@@ -1778,12 +1778,12 @@
       <c r="H7" s="141" t="n"/>
       <c r="I7" s="20" t="inlineStr">
         <is>
-          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao (PF, documentoFederal 97719943368) via bmp-onboarding-conta-solicitar</t>
+          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao (PF, documentoFederal 16113329666, Camila Rodrigues Teixeira, casada, cônjuge Diego Teixeira Costa CPF 80859537064, Belo Horizonte/MG)</t>
         </is>
       </c>
       <c r="J7" s="131" t="inlineStr">
         <is>
-          <t>HTTP 200 - {"codigoSolicitacao":"a780bd55-392f-4e58-aa90-d8d648793576"}. Documento enviado e solicitação finalizada com sucesso. Testado em 07/07/2026, homologação.</t>
+          <t>{"codigoSolicitacao":"15fa5349-d240-47f0-9d9e-bf389a64764d"} — HTTP 200, persistido (id 3)</t>
         </is>
       </c>
       <c r="K7" s="154" t="inlineStr">
@@ -1817,12 +1817,12 @@
       <c r="H8" s="150" t="n"/>
       <c r="I8" s="59" t="inlineStr">
         <is>
-          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao (PF, documentoFederal 97719943368) via bmp-onboarding-conta-solicitar</t>
+          <t>POST /v1/api/OnboardingContas/ContaSolicitacaoCriacao (PF, documentoFederal 22891544315, Bruno Cesar Nogueira, casado, cônjuge Larissa Nogueira Cardoso CPF 72141907535, Curitiba/PR)</t>
         </is>
       </c>
       <c r="J8" s="151" t="inlineStr">
         <is>
-          <t>HTTP 200 - {"codigoSolicitacao":"67999274-aba1-447f-8911-5bb56b9a6b72"}. Documento enviado e solicitação finalizada com sucesso. Testado em 07/07/2026, homologação.</t>
+          <t>{"codigoSolicitacao":"a28bf7e3-4a89-480c-9c30-44c7b0ec4e27"} — HTTP 200, persistido (id 4)</t>
         </is>
       </c>
       <c r="K8" s="155" t="inlineStr">
@@ -2008,23 +2008,23 @@
       <c r="H12" s="141" t="n"/>
       <c r="I12" s="20" t="inlineStr">
         <is>
-          <t>POST /v1/api/OnboardingContas/PessoasDocumentoArquivo (tipoEntidade=Correntista, tipoDocumento=Identificação/Termo aceite, arquivo base64, finalizarSolicitacao=true) via bmp-onboarding-documento-enviar</t>
+          <t>POST /v1/api/OnboardingContas/PessoasDocumentoArquivo — testado nas 4 contas casadas acima, com e sem 'finalizarSolicitacao' junto</t>
         </is>
       </c>
       <c r="J12" s="131" t="inlineStr">
         <is>
-          <t>HTTP 200 - documento enviado com sucesso, com finalização combinada na mesma chamada (checkbox "Finalizar junto com este envio"). Retestado em 07/07/2026 nas 4 novas solicitações do ciclo (20197582-..., 9e1cbba1-..., a780bd55-..., 67999274-...).</t>
+          <t>{"meta":null,"errors":[{"code":null,"title":null,"detail":"Não é possível inserir documento na situação atual da solicitação."}]} — HTTP 400, idêntico nas 4 contas, imediatamente após a criação (mesmo minuto)</t>
         </is>
       </c>
       <c r="K12" s="21" t="n"/>
       <c r="L12" s="237" t="inlineStr">
         <is>
-          <t>Implementado - testado, OK</t>
+          <t>Implementado - testado, BLOQUEADO (erro de negócio do BMP)</t>
         </is>
       </c>
       <c r="M12" s="237" t="inlineStr">
         <is>
-          <t>Function bmp-onboarding-documento-enviar retestada com sucesso em 07/07/2026, 4x consecutivas, já com o envio+finalização combinados em uma chamada.</t>
+          <t>ACHADO CONSOLIDADO (07/07/2026): o bloqueio 'Não é possível inserir documento na situação atual da solicitação' foi investigado a fundo nesta rodada e as seguintes causas foram descartadas com teste direto: (1) timing/fila assíncrona do BMP — reproduzido no mesmo minuto da criação da conta; (2) estado civil/dados de cônjuge incompletos — reproduzido com as 4 contas casadas e com nome+CPF do cônjuge preenchidos; (3) 'Finalizar junto' ausente — reproduzido com a opção marcada e desmarcada; (4) CPF do documento divergente da solicitação — corrigido bug de UI que causava isso (campo agora auto-preenche), erro persiste mesmo com CPF correto; (5) handshake HMAC — endpoints de Onboarding não constam na lista oficial de endpoints protegidos por handshake da doc BMP, então não se aplica; (6) mudança de código no Capt — comparado byte a byte o payload enviado num round que funcionou (mesmo dia, minutos antes) com o que falha agora: estrutura idêntica. Conclusão: bloqueio real do lado do BMP homologação, não reproduzível/corrigível via código Capt. BUG CORRIGIDO nesta rodada (efeito colateral, não a causa raiz): a function bmp-onboarding-documento-enviar marcava o status local como sucesso mesmo quando o BMP retornava erro — corrigido (só avança status em sucesso real confirmado). PRÓXIMO PASSO: reportar ao suporte BMP os códigos de solicitação e o erro exato para identificar a 'situação' exigida.</t>
         </is>
       </c>
       <c r="N12" s="237" t="inlineStr">
